--- a/attached_assets/kits.xlsx
+++ b/attached_assets/kits.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/85bbb62e3137b4e2/Desktop/Lab-Vault/Lab-Vault/attached_assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{056E80C1-7C3B-410B-B7F9-27B433DAE8B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="8_{056E80C1-7C3B-410B-B7F9-27B433DAE8B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F30B586D-67A9-4833-884E-21AA7842D825}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{843507C2-E488-4408-914D-2CABC8FB5163}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
   <si>
     <t xml:space="preserve">Name </t>
   </si>
@@ -42,30 +42,15 @@
     <t>Quantity</t>
   </si>
   <si>
-    <t>ARM Development Board: ARM7 board with LCD, UARTUSB, SDCARD,</t>
-  </si>
-  <si>
     <t>Texas MSP430-based Development board with Wi-Fi and LCD-interface.</t>
   </si>
   <si>
     <t>ESP-32-based Edu Robo board with two DC motors, dummy</t>
   </si>
   <si>
-    <t>Edu Robo board with two DC motors, dummy wheel, Wi-Fi,</t>
-  </si>
-  <si>
-    <t>NODEMCU-based IoT Sensor Interface (NodeMCU, LEDs,</t>
-  </si>
-  <si>
     <t>8051-based USB interface with LCD, Motor Driver, DAC</t>
   </si>
   <si>
-    <t>PIC18F4550-based USB interface with LCD, Motor Driver, DAC interface,</t>
-  </si>
-  <si>
-    <t>Atmega328-based Edu Robo board with two DC motors,</t>
-  </si>
-  <si>
     <t>ESP32-based mobile Embedded and IoT interfaces Testing platform</t>
   </si>
   <si>
@@ -82,6 +67,21 @@
   </si>
   <si>
     <t>Raspberry Pi Camera 3280x2464 static image</t>
+  </si>
+  <si>
+    <t>ARM Development Board: ARM7 board with LCD, UARTUSB, SDCARD</t>
+  </si>
+  <si>
+    <t>Edu Robo board with two DC motors, dummy wheel, Wi-Fi</t>
+  </si>
+  <si>
+    <t>NODEMCU-based IoT Sensor Interface (NodeMCU, LEDs)</t>
+  </si>
+  <si>
+    <t>PIC18F4550-based USB interface with LCD, Motor Driver, DAC interface</t>
+  </si>
+  <si>
+    <t>Atmega328-based Edu Robo board with two DC motors</t>
   </si>
 </sst>
 </file>
@@ -433,8 +433,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61DD3902-4DB1-4F03-A9AD-1C8E46753EBB}">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="62.21875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -446,7 +449,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B2">
         <v>3</v>
@@ -454,7 +457,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3">
         <v>3</v>
@@ -462,7 +465,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -470,7 +473,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B5">
         <v>3</v>
@@ -478,7 +481,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B6">
         <v>3</v>
@@ -486,7 +489,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B7">
         <v>3</v>
@@ -494,7 +497,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B8">
         <v>3</v>
@@ -502,7 +505,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B9">
         <v>2</v>
@@ -510,7 +513,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B10">
         <v>2</v>
@@ -518,7 +521,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -526,7 +529,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -534,7 +537,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B13">
         <v>2</v>
@@ -542,7 +545,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -550,7 +553,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -561,14 +564,6 @@
         <v>10</v>
       </c>
       <c r="B16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17">
         <v>6</v>
       </c>
     </row>
